--- a/artfynd/A 23220-2024 artfynd.xlsx
+++ b/artfynd/A 23220-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>117961881</v>
       </c>
       <c r="B3" t="n">
-        <v>104929</v>
+        <v>104931</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
